--- a/促音.xlsx
+++ b/促音.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="169">
   <si>
     <t>真っ直ぐ</t>
   </si>
@@ -807,13 +807,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1587,7 +1587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D87"/>
+  <dimension ref="A2:D88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
@@ -2311,6 +2311,14 @@
         <v>168</v>
       </c>
     </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/促音.xlsx
+++ b/促音.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="171">
   <si>
     <t>真っ直ぐ</t>
   </si>
@@ -634,6 +634,12 @@
   </si>
   <si>
     <t>けっしょう</t>
+  </si>
+  <si>
+    <t>熱する</t>
+  </si>
+  <si>
+    <t>ねっする</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D88"/>
+  <dimension ref="A2:D89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
@@ -2319,6 +2325,14 @@
         <v>95</v>
       </c>
     </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/促音.xlsx
+++ b/促音.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="171">
   <si>
     <t>真っ直ぐ</t>
   </si>
@@ -1593,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D89"/>
+  <dimension ref="A2:D90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
@@ -2333,6 +2333,14 @@
         <v>170</v>
       </c>
     </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/促音.xlsx
+++ b/促音.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="175">
   <si>
     <t>真っ直ぐ</t>
   </si>
@@ -640,6 +640,18 @@
   </si>
   <si>
     <t>ねっする</t>
+  </si>
+  <si>
+    <t>一斉に</t>
+  </si>
+  <si>
+    <t>いっせいに</t>
+  </si>
+  <si>
+    <t>圧縮</t>
+  </si>
+  <si>
+    <t>あっしゅく</t>
   </si>
 </sst>
 </file>
@@ -813,13 +825,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1593,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D90"/>
+  <dimension ref="A2:D92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
@@ -2341,6 +2353,22 @@
         <v>123</v>
       </c>
     </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/促音.xlsx
+++ b/促音.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="175">
   <si>
     <t>真っ直ぐ</t>
   </si>
@@ -1605,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D92"/>
+  <dimension ref="A2:D94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
@@ -2369,6 +2369,22 @@
         <v>174</v>
       </c>
     </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
